--- a/InputData/elec/RQSD/RPS Qualifying Source Definitions.xlsx
+++ b/InputData/elec/RQSD/RPS Qualifying Source Definitions.xlsx
@@ -1,24 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28227"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\elec\RQSD\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-india\InputData\elec\RQSD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CB7CAD8-F8F1-4C3C-99B7-2CAFF1F53D42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66CCDA7A-270B-4F30-85F5-6181862AB8C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="RQSD-BRQSD" sheetId="2" r:id="rId2"/>
     <sheet name="RQSD-RQSD" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'RQSD-RQSD'!$A$1:$B$18</definedName>
+  </definedNames>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -27,6 +33,7 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -34,18 +41,114 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="54">
+  <si>
+    <t>RQSD BAU RPS Qualifying Source Definitions</t>
+  </si>
+  <si>
+    <t>RQSD RPS Qualifying Source Definitions</t>
+  </si>
   <si>
     <t>Source:</t>
   </si>
   <si>
-    <t>Each U.S. state that has an RPS defines the sources that qualify for that RPS, leading to</t>
+    <t>Current RPOs</t>
+  </si>
+  <si>
+    <t>Existing State RPOs and compliance</t>
+  </si>
+  <si>
+    <t>Ministry of Power</t>
+  </si>
+  <si>
+    <t>Prayas Energy Group</t>
+  </si>
+  <si>
+    <t>Guidelines for long-term RPO growth trajectory of Renewable Purchase Obligations (RPOs) for non-solar as well as for solar - reg.</t>
+  </si>
+  <si>
+    <t>Renewable Energy Data Portal</t>
+  </si>
+  <si>
+    <t>https://www.mahaurja.com/meda/data/rporec/reports/MoP%20on%20Long%20term%20RPO%20trajectory.pdf</t>
+  </si>
+  <si>
+    <t>http://www.prayaspune.org/peg/rpos.html</t>
+  </si>
+  <si>
+    <t>Solar and non-solar targets and compliance, All States</t>
+  </si>
+  <si>
+    <t>RPO trajectory till 2022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hydro Power Obligations </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Union Cabinet/Press Information Bureau </t>
+  </si>
+  <si>
+    <t>Long term growth trajectory of RPOs for solar and non-solar for 2019-20 to 2021-22</t>
+  </si>
+  <si>
+    <t>Cabinet Approves Measures to Promote Hydro Power Sector</t>
+  </si>
+  <si>
+    <t>https://powermin.nic.in/sites/default/files/webform/notices/RPO_trajectory_2019-22_Order_dated_14_June_2018.pdf</t>
+  </si>
+  <si>
+    <t>https://pib.gov.in/pressreleaseshare.aspx?prid=1567817</t>
+  </si>
+  <si>
+    <t>Note:</t>
+  </si>
+  <si>
+    <t>India RPOs are differentiated by solar and non-solar (excluding hydro).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">For non-solar BAU RPOs, we include wind and biomass (as some states have RPO targets </t>
+  </si>
+  <si>
+    <t>for biomass). However, the compliance with targets has been low in most states.</t>
+  </si>
+  <si>
+    <t>For non-BAU/policy RPS qualifying source definitions, we include hydro, nuclear, and MSW</t>
+  </si>
+  <si>
+    <t>in addition to wind and solar as it may be useful for a more ambitious RE scenario with a delayed start.</t>
+  </si>
+  <si>
+    <t>Biomass is excluded because it is not truly carbon-neutral, and it has other issues, such as</t>
+  </si>
+  <si>
+    <t>local air quality, competing land use, and feedstock availability challenges.</t>
+  </si>
+  <si>
+    <t>Nuclear is included because it provides base load for the medium term until variable RE intermittency can be managed with storage. SMRs are included for similar reasons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hydro is included due to India's recent policy proposal to include large hydro as an RPO qualifying source. </t>
+  </si>
+  <si>
+    <t>Electricity Source</t>
+  </si>
+  <si>
+    <t>hard coal</t>
+  </si>
+  <si>
+    <t>natural gas steam turbine</t>
+  </si>
+  <si>
+    <t>naturla gas combined cycle</t>
   </si>
   <si>
     <t>nuclear</t>
   </si>
   <si>
     <t>hydro</t>
+  </si>
+  <si>
+    <t>onshore wind</t>
   </si>
   <si>
     <t>solar PV</t>
@@ -66,52 +169,10 @@
     <t>natural gas peaker</t>
   </si>
   <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>The non-BAU version of this variable supports a boolean policy lever and is intended to be set by the</t>
-  </si>
-  <si>
-    <t>RQSD BAU RPS Qualifying Source Definitions</t>
-  </si>
-  <si>
-    <t>RQSD RPS Qualifying Source Definitions</t>
-  </si>
-  <si>
     <t>lignite</t>
   </si>
   <si>
-    <t>hard coal</t>
-  </si>
-  <si>
-    <t>onshore wind</t>
-  </si>
-  <si>
     <t>offshore wind</t>
-  </si>
-  <si>
-    <t>differences between states.  Here, we use a "clean energy standard"</t>
-  </si>
-  <si>
-    <t>(counting everything except fossil fuels) as our definition for the BAU case.</t>
-  </si>
-  <si>
-    <t>model user.  The example we include uses only wind, solar, and geothermal.</t>
-  </si>
-  <si>
-    <t>Hydro is excluded because of limited potential for new large hydro and land use impacts.</t>
-  </si>
-  <si>
-    <t>Biomass is excluded because it is not truly carbon-neutral, and it has other issues, such as</t>
-  </si>
-  <si>
-    <t>local air quality impacts and land use challenges.</t>
-  </si>
-  <si>
-    <t>Nuclear is excluded because of the need to manage nuclear waste.</t>
-  </si>
-  <si>
-    <t>see notes</t>
   </si>
   <si>
     <t>crude oil</t>
@@ -121,15 +182,6 @@
   </si>
   <si>
     <t>municipal solid waste</t>
-  </si>
-  <si>
-    <t>Qualifies for RPS (Boolean)</t>
-  </si>
-  <si>
-    <t>natural gas steam turbine</t>
-  </si>
-  <si>
-    <t>natural gas combined cycle</t>
   </si>
   <si>
     <t>hard coal w CCS</t>
@@ -157,7 +209,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -188,13 +240,26 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -210,16 +275,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -525,86 +595,176 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="84.5703125" customWidth="1"/>
+    <col min="4" max="4" width="73.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="1"/>
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B6" s="2">
+        <v>2016</v>
+      </c>
+      <c r="D6" s="2">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B10" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="D10" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B5" s="2"/>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="1"/>
+      <c r="B12" s="2">
+        <v>2018</v>
+      </c>
+      <c r="D12" s="2">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B14" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B15" s="3"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
         <v>19</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+    <row r="23" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>24</v>
       </c>
     </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" s="7"/>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B8" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="B14" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -616,2412 +776,3079 @@
   <dimension ref="A1:AE25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.42578125" customWidth="1"/>
-    <col min="2" max="2" width="28.42578125" customWidth="1"/>
+    <col min="1" max="1" width="29.7109375" customWidth="1"/>
+    <col min="2" max="2" width="27.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="3">
+      <c r="B1" s="4">
         <v>2021</v>
       </c>
-      <c r="C1" s="3">
+      <c r="C1" s="4">
         <v>2022</v>
       </c>
-      <c r="D1" s="3">
+      <c r="D1" s="4">
         <v>2023</v>
       </c>
-      <c r="E1" s="3">
+      <c r="E1" s="4">
         <v>2024</v>
       </c>
-      <c r="F1" s="3">
+      <c r="F1" s="4">
         <v>2025</v>
       </c>
-      <c r="G1" s="3">
+      <c r="G1" s="4">
         <v>2026</v>
       </c>
-      <c r="H1" s="3">
+      <c r="H1" s="4">
         <v>2027</v>
       </c>
-      <c r="I1" s="3">
+      <c r="I1" s="4">
         <v>2028</v>
       </c>
-      <c r="J1" s="3">
+      <c r="J1" s="4">
         <v>2029</v>
       </c>
-      <c r="K1" s="3">
+      <c r="K1" s="4">
         <v>2030</v>
       </c>
-      <c r="L1" s="3">
+      <c r="L1" s="4">
         <v>2031</v>
       </c>
-      <c r="M1" s="3">
+      <c r="M1" s="4">
         <v>2032</v>
       </c>
-      <c r="N1" s="3">
+      <c r="N1" s="4">
         <v>2033</v>
       </c>
-      <c r="O1" s="3">
+      <c r="O1" s="4">
         <v>2034</v>
       </c>
-      <c r="P1" s="3">
+      <c r="P1" s="4">
         <v>2035</v>
       </c>
-      <c r="Q1" s="3">
+      <c r="Q1" s="4">
         <v>2036</v>
       </c>
-      <c r="R1" s="3">
+      <c r="R1" s="4">
         <v>2037</v>
       </c>
-      <c r="S1" s="3">
+      <c r="S1" s="4">
         <v>2038</v>
       </c>
-      <c r="T1" s="3">
+      <c r="T1" s="4">
         <v>2039</v>
       </c>
-      <c r="U1" s="3">
+      <c r="U1" s="4">
         <v>2040</v>
       </c>
-      <c r="V1" s="3">
+      <c r="V1" s="4">
         <v>2041</v>
       </c>
-      <c r="W1" s="3">
+      <c r="W1" s="4">
         <v>2042</v>
       </c>
-      <c r="X1" s="3">
+      <c r="X1" s="4">
         <v>2043</v>
       </c>
-      <c r="Y1" s="3">
+      <c r="Y1" s="4">
         <v>2044</v>
       </c>
-      <c r="Z1" s="3">
+      <c r="Z1" s="4">
         <v>2045</v>
       </c>
-      <c r="AA1" s="3">
+      <c r="AA1" s="4">
         <v>2046</v>
       </c>
-      <c r="AB1" s="3">
+      <c r="AB1" s="4">
         <v>2047</v>
       </c>
-      <c r="AC1" s="3">
+      <c r="AC1" s="4">
         <v>2048</v>
       </c>
-      <c r="AD1" s="3">
+      <c r="AD1" s="4">
         <v>2049</v>
       </c>
-      <c r="AE1" s="3">
+      <c r="AE1" s="4">
         <v>2050</v>
       </c>
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
+        <f>$B2</f>
         <v>0</v>
       </c>
       <c r="D2">
+        <f t="shared" ref="D2:AE11" si="0">$B2</f>
         <v>0</v>
       </c>
       <c r="E2">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F2">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G2">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H2">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I2">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J2">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K2">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L2">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="M2">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="N2">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="O2">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="P2">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Q2">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R2">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S2">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T2">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="U2">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="V2">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="W2">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="X2">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Y2">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Z2">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AA2">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AB2">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AC2">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AD2">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AE2">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B3">
         <v>0</v>
       </c>
       <c r="C3">
+        <f t="shared" ref="C3:R25" si="1">$B3</f>
         <v>0</v>
       </c>
       <c r="D3">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="E3">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F3">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G3">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H3">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I3">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J3">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K3">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L3">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M3">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N3">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="O3">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="P3">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Q3">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R3">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S3">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T3">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="U3">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="V3">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="W3">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="X3">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Y3">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Z3">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AA3">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AB3">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AC3">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AD3">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AE3">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B4">
         <v>0</v>
       </c>
       <c r="C4">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D4">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E4">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F4">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G4">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H4">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I4">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J4">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K4">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L4">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="M4">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="N4">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="O4">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="P4">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Q4">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R4">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S4">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T4">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="U4">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="V4">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="W4">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="X4">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Y4">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Z4">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AA4">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AB4">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AC4">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AD4">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AE4">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="K5">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="L5">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="M5">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="N5">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="O5">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="Q5">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="R5">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="S5">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="T5">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="V5">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="W5">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="X5">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="Y5">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="Z5">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="AA5">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="AB5">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="AC5">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="AD5">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="AE5">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="L6">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="M6">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="N6">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="O6">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="Q6">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="R6">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="S6">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="T6">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="U6">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="V6">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="W6">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="X6">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="Y6">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="Z6">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="AA6">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="AB6">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="AC6">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="AD6">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="AE6">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7">
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="D7">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E7">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="F7">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="G7">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="H7">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="I7">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="J7">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="K7">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="L7">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="M7">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="N7">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="O7">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="P7">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="Q7">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="R7">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="S7">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="T7">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="U7">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="V7">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="W7">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="X7">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="Y7">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="Z7">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AA7">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AB7">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AC7">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AD7">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AE7">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
       <c r="C8">
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="D8">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E8">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="F8">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="G8">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="H8">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="I8">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="J8">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="K8">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="L8">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="M8">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="N8">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="O8">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="P8">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="Q8">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="R8">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="S8">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="T8">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="U8">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="V8">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="W8">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="X8">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="Y8">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="Z8">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AA8">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AB8">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AC8">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AD8">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AE8">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
       <c r="C9">
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="D9">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E9">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="F9">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="G9">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="H9">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="I9">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="J9">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="K9">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="L9">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="M9">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="N9">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="O9">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="P9">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="Q9">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="R9">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="S9">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="T9">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="U9">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="V9">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="W9">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="X9">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="Y9">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="Z9">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AA9">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AB9">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AC9">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AD9">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AE9">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="B10">
         <v>1</v>
       </c>
       <c r="C10">
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="D10">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E10">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="F10">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="G10">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="H10">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="I10">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="J10">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="K10">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="L10">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="M10">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="N10">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="O10">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="P10">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="Q10">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="R10">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="S10">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="T10">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="U10">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="V10">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="W10">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="X10">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="Y10">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="Z10">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AA10">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AB10">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AC10">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AD10">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AE10">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="B11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C11">
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="F11">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="H11">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="I11">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="K11">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="L11">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="M11">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="N11">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="O11">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="P11">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="Q11">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="R11">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="S11">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="T11">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="U11">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="V11">
-        <v>1</v>
+        <f t="shared" ref="D11:AE20" si="2">$B11</f>
+        <v>0</v>
       </c>
       <c r="W11">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="X11">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="Y11">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="Z11">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="AA11">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="AB11">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="AC11">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="AD11">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="AE11">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="B12">
         <v>0</v>
       </c>
       <c r="C12">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D12">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="E12">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F12">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G12">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H12">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I12">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J12">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K12">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L12">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M12">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="N12">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O12">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="P12">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Q12">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="R12">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S12">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="T12">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="U12">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="V12">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W12">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="X12">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y12">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Z12">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AA12">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AB12">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AC12">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AD12">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AE12">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="B13">
         <v>0</v>
       </c>
       <c r="C13">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D13">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="E13">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F13">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G13">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H13">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I13">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J13">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K13">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L13">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M13">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="N13">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O13">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="P13">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Q13">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="R13">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S13">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="T13">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="U13">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="V13">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W13">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="X13">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y13">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Z13">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AA13">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AB13">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AC13">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AD13">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AE13">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="B14">
         <f>B2</f>
         <v>0</v>
       </c>
       <c r="C14">
-        <f t="shared" ref="C14:AE14" si="0">C2</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="E14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="N14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="P14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Q14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="R14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="T14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="U14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="V14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="X14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Z14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AA14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AB14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AC14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AD14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AE14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="B15">
         <v>1</v>
       </c>
       <c r="C15">
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="D15">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="E15">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="F15">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G15">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H15">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="I15">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="J15">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="K15">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="L15">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="M15">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="N15">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="O15">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="P15">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="Q15">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="R15">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="S15">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="T15">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="U15">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="V15">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="W15">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="X15">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="Y15">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="Z15">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AA15">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AB15">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AC15">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AD15">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AE15">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="B16">
         <v>0</v>
       </c>
       <c r="C16">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D16">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="E16">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F16">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G16">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H16">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I16">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J16">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K16">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L16">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M16">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="N16">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O16">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="P16">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Q16">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="R16">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S16">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="T16">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="U16">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="V16">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W16">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="X16">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y16">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Z16">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AA16">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AB16">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AC16">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AD16">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AE16">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="B17">
         <v>0</v>
       </c>
       <c r="C17">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D17">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="E17">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F17">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G17">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H17">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I17">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J17">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K17">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L17">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M17">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="N17">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O17">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="P17">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Q17">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="R17">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S17">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="T17">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="U17">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="V17">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W17">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="X17">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y17">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Z17">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AA17">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AB17">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AC17">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AD17">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AE17">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="B18">
         <v>0</v>
       </c>
       <c r="C18">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D18">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="E18">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F18">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G18">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H18">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I18">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J18">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K18">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L18">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M18">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="N18">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O18">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="P18">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Q18">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="R18">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S18">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="T18">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="U18">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="V18">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W18">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="X18">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y18">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Z18">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AA18">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AB18">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AC18">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AD18">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AE18">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="B19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C19">
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="D19">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="F19">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="G19">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="H19">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="I19">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="J19">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="K19">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="L19">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="M19">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="N19">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="O19">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="P19">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="Q19">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="R19">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="S19">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="T19">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="U19">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="V19">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="W19">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="X19">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="Y19">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="Z19">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="AA19">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="AB19">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="AC19">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="AD19">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="AE19">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="B20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20">
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="D20">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="F20">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="G20">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="H20">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="I20">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="J20">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="K20">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="L20">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="M20">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="N20">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="O20">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="P20">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="Q20">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="R20">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="S20">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="T20">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="U20">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="V20">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="W20">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="X20">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="Y20">
-        <v>1</v>
+        <f t="shared" ref="D20:AE25" si="3">$B20</f>
+        <v>0</v>
       </c>
       <c r="Z20">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="AA20">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="AB20">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="AC20">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="AD20">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="AE20">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="B21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C21">
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="D21">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="F21">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="G21">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="H21">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="I21">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="J21">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="K21">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="L21">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="M21">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="N21">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="O21">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="P21">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="Q21">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="R21">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="S21">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="T21">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="U21">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="V21">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="W21">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="X21">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="Y21">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="Z21">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="AA21">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="AB21">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="AC21">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="AD21">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="AE21">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="B22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C22">
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="D22">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="F22">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="G22">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="H22">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="I22">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="J22">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="K22">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="L22">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="M22">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="N22">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="O22">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="P22">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="Q22">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="R22">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="S22">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="T22">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="U22">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="V22">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="W22">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="X22">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="Y22">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="Z22">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="AA22">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="AB22">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="AC22">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="AD22">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="AE22">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="B23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C23">
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="D23">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="F23">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="G23">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="H23">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="I23">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="J23">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="K23">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="L23">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="M23">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="N23">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="O23">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="P23">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="Q23">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="R23">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="S23">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="T23">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="U23">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="V23">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="W23">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="X23">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="Y23">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="Z23">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="AA23">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="AB23">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="AC23">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="AD23">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="AE23">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>37</v>
+      <c r="A24" s="6" t="s">
+        <v>52</v>
       </c>
       <c r="B24">
         <v>1</v>
       </c>
       <c r="C24">
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="D24">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="E24">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="F24">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="G24">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="H24">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="I24">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="J24">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="K24">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="L24">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="M24">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="N24">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="O24">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="P24">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="Q24">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="R24">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="S24">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="T24">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="U24">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="V24">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="W24">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="X24">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="Y24">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="Z24">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="AA24">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="AB24">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="AC24">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="AD24">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="AE24">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
-        <v>38</v>
+      <c r="A25" s="6" t="s">
+        <v>53</v>
       </c>
       <c r="B25">
         <v>1</v>
       </c>
       <c r="C25">
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="D25">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="E25">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="F25">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="G25">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="H25">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="I25">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="J25">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="K25">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="L25">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="M25">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="N25">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="O25">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="P25">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="Q25">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="R25">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="S25">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="T25">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="U25">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="V25">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="W25">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="X25">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="Y25">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="Z25">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="AA25">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="AB25">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="AC25">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="AD25">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="AE25">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -3038,2416 +3865,3277 @@
   <dimension ref="A1:AE25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.42578125" customWidth="1"/>
-    <col min="2" max="2" width="28.42578125" customWidth="1"/>
+    <col min="1" max="1" width="29.7109375" customWidth="1"/>
+    <col min="2" max="2" width="27.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="3">
+      <c r="B1" s="4">
         <v>2021</v>
       </c>
-      <c r="C1" s="3">
+      <c r="C1" s="4">
         <v>2022</v>
       </c>
-      <c r="D1" s="3">
+      <c r="D1" s="4">
         <v>2023</v>
       </c>
-      <c r="E1" s="3">
+      <c r="E1" s="4">
         <v>2024</v>
       </c>
-      <c r="F1" s="3">
+      <c r="F1" s="4">
         <v>2025</v>
       </c>
-      <c r="G1" s="3">
+      <c r="G1" s="4">
         <v>2026</v>
       </c>
-      <c r="H1" s="3">
+      <c r="H1" s="4">
         <v>2027</v>
       </c>
-      <c r="I1" s="3">
+      <c r="I1" s="4">
         <v>2028</v>
       </c>
-      <c r="J1" s="3">
+      <c r="J1" s="4">
         <v>2029</v>
       </c>
-      <c r="K1" s="3">
+      <c r="K1" s="4">
         <v>2030</v>
       </c>
-      <c r="L1" s="3">
+      <c r="L1" s="4">
         <v>2031</v>
       </c>
-      <c r="M1" s="3">
+      <c r="M1" s="4">
         <v>2032</v>
       </c>
-      <c r="N1" s="3">
+      <c r="N1" s="4">
         <v>2033</v>
       </c>
-      <c r="O1" s="3">
+      <c r="O1" s="4">
         <v>2034</v>
       </c>
-      <c r="P1" s="3">
+      <c r="P1" s="4">
         <v>2035</v>
       </c>
-      <c r="Q1" s="3">
+      <c r="Q1" s="4">
         <v>2036</v>
       </c>
-      <c r="R1" s="3">
+      <c r="R1" s="4">
         <v>2037</v>
       </c>
-      <c r="S1" s="3">
+      <c r="S1" s="4">
         <v>2038</v>
       </c>
-      <c r="T1" s="3">
+      <c r="T1" s="4">
         <v>2039</v>
       </c>
-      <c r="U1" s="3">
+      <c r="U1" s="4">
         <v>2040</v>
       </c>
-      <c r="V1" s="3">
+      <c r="V1" s="4">
         <v>2041</v>
       </c>
-      <c r="W1" s="3">
+      <c r="W1" s="4">
         <v>2042</v>
       </c>
-      <c r="X1" s="3">
+      <c r="X1" s="4">
         <v>2043</v>
       </c>
-      <c r="Y1" s="3">
+      <c r="Y1" s="4">
         <v>2044</v>
       </c>
-      <c r="Z1" s="3">
+      <c r="Z1" s="4">
         <v>2045</v>
       </c>
-      <c r="AA1" s="3">
+      <c r="AA1" s="4">
         <v>2046</v>
       </c>
-      <c r="AB1" s="3">
+      <c r="AB1" s="4">
         <v>2047</v>
       </c>
-      <c r="AC1" s="3">
+      <c r="AC1" s="4">
         <v>2048</v>
       </c>
-      <c r="AD1" s="3">
+      <c r="AD1" s="4">
         <v>2049</v>
       </c>
-      <c r="AE1" s="3">
+      <c r="AE1" s="4">
         <v>2050</v>
       </c>
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
+        <f>$B2</f>
         <v>0</v>
       </c>
       <c r="D2">
+        <f t="shared" ref="D2:AE11" si="0">$B2</f>
         <v>0</v>
       </c>
       <c r="E2">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F2">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G2">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H2">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I2">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J2">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K2">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L2">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="M2">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="N2">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="O2">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="P2">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Q2">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R2">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S2">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T2">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="U2">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="V2">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="W2">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="X2">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Y2">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Z2">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AA2">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AB2">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AC2">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AD2">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AE2">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B3">
         <v>0</v>
       </c>
       <c r="C3">
+        <f t="shared" ref="C3:R25" si="1">$B3</f>
         <v>0</v>
       </c>
       <c r="D3">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="E3">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F3">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G3">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H3">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I3">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J3">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K3">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L3">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M3">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N3">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="O3">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="P3">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Q3">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R3">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S3">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T3">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="U3">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="V3">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="W3">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="X3">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Y3">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Z3">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AA3">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AB3">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AC3">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AD3">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AE3">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B4">
         <v>0</v>
       </c>
       <c r="C4">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D4">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E4">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F4">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G4">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H4">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I4">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J4">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K4">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L4">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="M4">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="N4">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="O4">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="P4">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Q4">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R4">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S4">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T4">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="U4">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="V4">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="W4">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="X4">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Y4">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Z4">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AA4">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AB4">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AC4">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AD4">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AE4">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7">
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="D7">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E7">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="F7">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="G7">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="H7">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="I7">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="J7">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="K7">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="L7">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="M7">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="N7">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="O7">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="P7">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="Q7">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="R7">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="S7">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="T7">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="U7">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="V7">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="W7">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="X7">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="Y7">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="Z7">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AA7">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AB7">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AC7">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AD7">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AE7">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
       <c r="C8">
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="D8">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E8">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="F8">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="G8">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="H8">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="I8">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="J8">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="K8">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="L8">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="M8">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="N8">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="O8">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="P8">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="Q8">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="R8">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="S8">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="T8">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="U8">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="V8">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="W8">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="X8">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="Y8">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="Z8">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AA8">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AB8">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AC8">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AD8">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AE8">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
       <c r="C9">
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="D9">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E9">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="F9">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="G9">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="H9">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="I9">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="J9">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="K9">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="L9">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="M9">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="N9">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="O9">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="P9">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="Q9">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="R9">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="S9">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="T9">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="U9">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="V9">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="W9">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="X9">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="Y9">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="Z9">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AA9">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AB9">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AC9">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AD9">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AE9">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="B10">
         <v>0</v>
       </c>
       <c r="C10">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="M10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="N10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="O10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="P10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Q10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="U10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="V10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="W10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="X10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Y10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Z10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AA10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AB10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AC10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AD10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AE10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="B11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C11">
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="F11">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="H11">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="I11">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="K11">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="L11">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="M11">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="N11">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="O11">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="P11">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="Q11">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="R11">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="S11">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="T11">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="U11">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="V11">
-        <v>1</v>
+        <f t="shared" ref="D11:AE20" si="2">$B11</f>
+        <v>0</v>
       </c>
       <c r="W11">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="X11">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="Y11">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="Z11">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="AA11">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="AB11">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="AC11">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="AD11">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="AE11">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="B12">
         <v>0</v>
       </c>
       <c r="C12">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D12">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="E12">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F12">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G12">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H12">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I12">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J12">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K12">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L12">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M12">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="N12">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O12">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="P12">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Q12">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="R12">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S12">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="T12">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="U12">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="V12">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W12">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="X12">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y12">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Z12">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AA12">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AB12">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AC12">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AD12">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AE12">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="B13">
         <v>0</v>
       </c>
       <c r="C13">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D13">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="E13">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F13">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G13">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H13">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I13">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J13">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K13">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L13">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M13">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="N13">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O13">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="P13">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Q13">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="R13">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S13">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="T13">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="U13">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="V13">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W13">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="X13">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y13">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Z13">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AA13">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AB13">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AC13">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AD13">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AE13">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="B14">
         <f>B2</f>
         <v>0</v>
       </c>
       <c r="C14">
-        <f t="shared" ref="C14:AE14" si="0">C2</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="E14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="N14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="P14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Q14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="R14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="T14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="U14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="V14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="X14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Z14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AA14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AB14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AC14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AD14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AE14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="B15">
         <v>1</v>
       </c>
       <c r="C15">
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="D15">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="E15">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="F15">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G15">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H15">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="I15">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="J15">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="K15">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="L15">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="M15">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="N15">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="O15">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="P15">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="Q15">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="R15">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="S15">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="T15">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="U15">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="V15">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="W15">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="X15">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="Y15">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="Z15">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AA15">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AB15">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AC15">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AD15">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AE15">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="B16">
         <v>0</v>
       </c>
       <c r="C16">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D16">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="E16">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F16">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G16">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H16">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I16">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J16">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K16">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L16">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M16">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="N16">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O16">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="P16">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Q16">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="R16">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S16">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="T16">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="U16">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="V16">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W16">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="X16">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y16">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Z16">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AA16">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AB16">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AC16">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AD16">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AE16">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="B17">
         <v>0</v>
       </c>
       <c r="C17">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D17">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="E17">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F17">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G17">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H17">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I17">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J17">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K17">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L17">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M17">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="N17">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O17">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="P17">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Q17">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="R17">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S17">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="T17">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="U17">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="V17">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W17">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="X17">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y17">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Z17">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AA17">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AB17">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AC17">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AD17">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AE17">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="N18">
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="B19">
         <v>0</v>
       </c>
       <c r="C19">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D19">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="E19">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F19">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G19">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H19">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I19">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J19">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K19">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L19">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M19">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="N19">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O19">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="P19">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Q19">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="R19">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S19">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="T19">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="U19">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="V19">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W19">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="X19">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y19">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Z19">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AA19">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AB19">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AC19">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AD19">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AE19">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="B20">
         <v>0</v>
       </c>
       <c r="C20">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D20">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="E20">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F20">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G20">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H20">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I20">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J20">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K20">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L20">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M20">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="N20">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O20">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="P20">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Q20">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="R20">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S20">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="T20">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="U20">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="V20">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W20">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="X20">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y20">
+        <f t="shared" ref="D20:AE25" si="3">$B20</f>
         <v>0</v>
       </c>
       <c r="Z20">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AA20">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AB20">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AC20">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AD20">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AE20">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
       <c r="M21">
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
       <c r="N21">
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="B22">
         <v>0</v>
       </c>
       <c r="C22">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D22">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E22">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="F22">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G22">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H22">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I22">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J22">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K22">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L22">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M22">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N22">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="O22">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="P22">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Q22">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="R22">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S22">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="T22">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="U22">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="V22">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="W22">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="X22">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Y22">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Z22">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AA22">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AB22">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AC22">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AD22">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AE22">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
       <c r="G23">
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
       <c r="M23">
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
       <c r="N23">
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>37</v>
+      <c r="A24" s="6" t="s">
+        <v>52</v>
       </c>
       <c r="B24">
         <v>1</v>
       </c>
       <c r="C24">
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="D24">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="E24">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="F24">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="G24">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="H24">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="I24">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="J24">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="K24">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="L24">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="M24">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="N24">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="O24">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="P24">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="Q24">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="R24">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="S24">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="T24">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="U24">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="V24">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="W24">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="X24">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="Y24">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="Z24">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="AA24">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="AB24">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="AC24">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="AD24">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="AE24">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
-        <v>38</v>
+      <c r="A25" s="6" t="s">
+        <v>53</v>
       </c>
       <c r="B25">
         <v>1</v>
       </c>
       <c r="C25">
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="D25">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="E25">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="F25">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="G25">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="H25">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="I25">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="J25">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="K25">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="L25">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="M25">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="N25">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="O25">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="P25">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="Q25">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="R25">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="S25">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="T25">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="U25">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="V25">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="W25">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="X25">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="Y25">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="Z25">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="AA25">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="AB25">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="AC25">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="AD25">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="AE25">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A251C7805F896F47A4F48569C73A0799" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="77cd1fc208aa16a525090c2a27f33c66">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d77402130d0e9b5bbfbb66ed18db98d9" ns2:_="">
+    <xsd:import namespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="11" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{65F91381-EE08-4624-A9D3-5F10486C2C9D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D95AA55E-3A2F-4513-8A2A-FD0AC76AE3C4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B3F7B30-2DD2-4176-93EF-222B90F66C44}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="f3083de3-5d4e-49f2-a3cd-0aeb079e6739"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>